--- a/Output/OBC Andolan/extracted_links.xlsx
+++ b/Output/OBC Andolan/extracted_links.xlsx
@@ -487,14 +487,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/education-today/news/story/reservation-beyond-50-mps-obc-demand-faces-judicial-scrutiny-2781436-2025-09-04</t>
+          <t>https://impressivetimes.com/latest/congress-demands-reservation-private-educational-institutions/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/congress-demands-reservation-private-educational-institutions/</t>
+          <t>https://www.indiatoday.in/education-today/news/story/reservation-beyond-50-mps-obc-demand-faces-judicial-scrutiny-2781436-2025-09-04</t>
         </is>
       </c>
     </row>
@@ -550,126 +550,126 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maratha-quota-manoj-jarange-warns-if-betrayed-ruling-parties-will-bite-dust-in-polls-stir-to-continue-in-konkan/articleshow/123714122.cms</t>
+          <t>https://m.thewire.in/article/politics/maratha-reservation-row-highlights-differences-within-bjp-led-mahayuti-govt-in-maharashtra/amp</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/politics/maratha-reservation-row-highlights-differences-within-bjp-led-mahayuti-govt-in-maharashtra/amp</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/04/maharashtra-congress-urges-cm-fadnavis-to-raise-obc-quota-from-27-to-42-on-telangana-model</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/04/maharashtra-congress-urges-cm-fadnavis-to-raise-obc-quota-from-27-to-42-on-telangana-model</t>
+          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1291262</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1291262</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maratha-quota-agitation-activists-end-protest-as-govt-assures-their-quota-would-remain-untouched-3711729</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maratha-quota-agitation-activists-end-protest-as-govt-assures-their-quota-would-remain-untouched-3711729</t>
+          <t>https://english.lokshahi.com/latest-news/fadnavis-breaks-silence-no-injustice-to-obcs-in-hyderabad-gazetteer-gr</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/latest-news/fadnavis-breaks-silence-no-injustice-to-obcs-in-hyderabad-gazetteer-gr</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/sakal-obc-samaj-urges-govt-not-to-yield-to-maratha-quota-demands/articleshow/123619015.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/sakal-obc-samaj-urges-govt-not-to-yield-to-maratha-quota-demands/articleshow/123619015.cms</t>
+          <t>https://www.indiatoday.in/india/story/maratha-quota-protest-mumbai-is-manoj-jarange-patil-really-a-achievement-big-historic-win-explained-voices-2781290-2025-09-03</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maratha-quota-protest-mumbai-is-manoj-jarange-patil-really-a-achievement-big-historic-win-explained-voices-2781290-2025-09-03</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/will-ask-obcs-to-come-under-open-category-cong-mla-wadettiwar/articleshow/123724689.cms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/will-ask-obcs-to-come-under-open-category-cong-mla-wadettiwar/articleshow/123724689.cms</t>
+          <t>https://www.devdiscourse.com/article/law-order/3615789-maharashtras-balancing-act-maratha-reservation-and-obc-safeguards</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3615789-maharashtras-balancing-act-maratha-reservation-and-obc-safeguards</t>
+          <t>https://www.deccanherald.com/india/maharashtra/devendra-fadnavis-assures-chhagan-bhujbal-of-no-injustice-to-obcs-day-after-ncp-leader-skips-cabinet-meet-maratha-reservation-issue-3712298</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/devendra-fadnavis-assures-chhagan-bhujbal-of-no-injustice-to-obcs-day-after-ncp-leader-skips-cabinet-meet-maratha-reservation-issue-3712298</t>
+          <t>https://www.siasat.com/will-fadnavis-govt-follow-telangana-model-and-grant-42-pc-quota-to-obcs-asks-sapkal-3267706/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/will-fadnavis-govt-follow-telangana-model-and-grant-42-pc-quota-to-obcs-asks-sapkal-3267706/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/have-faith-our-people-in-marathwada-and-western-maharashtra-will-get-reservation-jarange-3709943</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/have-faith-our-people-in-marathwada-and-western-maharashtra-will-get-reservation-jarange-3709943</t>
+          <t>https://www.newindianexpress.com/amp/story/nation/2025/Sep/04/maharashtra-cm-fadnavis-assures-obcs-that-maratha-quota-move-wont-affect-their-reservations</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/amp/story/nation/2025/Sep/04/maharashtra-cm-fadnavis-assures-obcs-that-maratha-quota-move-wont-affect-their-reservations</t>
+          <t>https://english.gujaratsamachar.com/news/gujarat/bjp-mla-says-most-of-the-benefits-of-obc-are-availed-by-affluent-castes-sparks-controversy</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://english.gujaratsamachar.com/news/gujarat/bjp-mla-says-most-of-the-benefits-of-obc-are-availed-by-affluent-castes-sparks-controversy</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maratha-quota-issue-maharashtra-minister-chhagan-bhujbal-boycotts-cabinet-meet-3709912</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maratha-quota-issue-maharashtra-minister-chhagan-bhujbal-boycotts-cabinet-meet-3709912</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/04/if-betrayed-over-maratha-quota-we-will-make-them-bite-the-dust-in-polls-jarange-2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/04/if-betrayed-over-maratha-quota-we-will-make-them-bite-the-dust-in-polls-jarange-2</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/obc-federation-sees-no-loss-in-maratha-gr-but-demands-talks-before-ending-stir/articleshow/123684651.cms</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/obc-federation-sees-no-loss-in-maratha-gr-but-demands-talks-before-ending-stir/articleshow/123684651.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maratha-quota-protest-in-mumbai-stop-pampering-jarange-bhujbal-tells-maharashtra-government-warns-of-obc-protest-if-demands-met/articleshow/123621077.cms</t>
         </is>
       </c>
     </row>
@@ -690,91 +690,91 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maratha-quota-protest-in-mumbai-stop-pampering-jarange-bhujbal-tells-maharashtra-government-warns-of-obc-protest-if-demands-met/articleshow/123621077.cms</t>
+          <t>https://www.thestatesman.com/india/congress-demands-law-for-reservation-in-private-educational-institutions-1503481991.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/congress-demands-law-for-reservation-in-private-educational-institutions-1503481991.html</t>
+          <t>https://aninews.in/news/national/general-news/gross-betrayal-breach-of-trust-and-violation-of-social-justice-sravan-dasoju-accuses-centre-ugc-of-failing-to-enforce-bc-reservations20250905225143/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/gross-betrayal-breach-of-trust-and-violation-of-social-justice-sravan-dasoju-accuses-centre-ugc-of-failing-to-enforce-bc-reservations20250905225143/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maratha-reservation-issue-settled-bhujbal-was-also-informed-by-cm-eknath-shinde-10230971/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maratha-reservation-issue-settled-bhujbal-was-also-informed-by-cm-eknath-shinde-10230971/</t>
+          <t>https://zeenews.india.com/india/no-intent-to-take-away-reservation-of-one-community-and-giving-to-another-cm-fadnavis-2955596.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/no-intent-to-take-away-reservation-of-one-community-and-giving-to-another-cm-fadnavis-2955596.html</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/03/maratha-community-divided-as-maharashtra-government-issues-gr-on-kunbi-certificates-under-obc-quota</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/03/maratha-community-divided-as-maharashtra-government-issues-gr-on-kunbi-certificates-under-obc-quota</t>
+          <t>https://www.devdiscourse.com/article/law-order/3613986-maharashtras-maratha-reservation-protest-a-tug-of-obc-identity</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3613986-maharashtras-maratha-reservation-protest-a-tug-of-obc-identity</t>
+          <t>https://punemirror.com/news/gr-on-quota-illegal-activist-laxman-hake-warns-obcs-may-move-court/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://punemirror.com/news/gr-on-quota-illegal-activist-laxman-hake-warns-obcs-may-move-court/</t>
+          <t>https://www.asianage.com/nation/maratha-obc-quota-dispute-sparks-tensions-within-maha-government-1901459</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.asianage.com/nation/maratha-obc-quota-dispute-sparks-tensions-within-maha-government-1901459</t>
+          <t>https://punemirror.com/opinion/editorials/reservation-riddle-maratha-quota-and-the-obc-conundrum/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://punemirror.com/opinion/editorials/reservation-riddle-maratha-quota-and-the-obc-conundrum/</t>
+          <t>https://www.indianewsstream.com/obcs-must-fight-their-own-battle-instead-of-relying-on-any-leader-prakash-ambedkar/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.news18.com/videos/breaking-news/maharashtra-protests-over-maratha-reservation-discontent-obc-groups-voice-discontent-news18-9545908.html</t>
+          <t>https://english.lokshahi.com/latest-news/chandrashekhar-bawankule-first-reaction-responsibility-of-the-chairmanship-of-the-obc-sub-committee-in-the-cabinet-ministry-maratha-reservation</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.indianewsstream.com/obcs-must-fight-their-own-battle-instead-of-relying-on-any-leader-prakash-ambedkar/</t>
+          <t>https://www.news18.com/videos/breaking-news/maharashtra-protests-over-maratha-reservation-discontent-obc-groups-voice-discontent-news18-9545908.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/latest-news/chandrashekhar-bawankule-first-reaction-responsibility-of-the-chairmanship-of-the-obc-sub-committee-in-the-cabinet-ministry-maratha-reservation</t>
+          <t>https://www.indiatoday.in/india/story/what-is-the-hyderabad-gazette-giving-reservation-to-marathas-kunbi-status-maharashtra-government-maratha-quota-row-2781342-2025-09-03</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/what-is-the-hyderabad-gazette-giving-reservation-to-marathas-kunbi-status-maharashtra-government-maratha-quota-row-2781342-2025-09-03</t>
+          <t>https://indianexpress.com/article/cities/mumbai/mumbai-maratha-quota-protest-live-updates-manoj-jarange-patil-hunger-strike-fadnavis-cabinet-10223256/</t>
         </is>
       </c>
     </row>
@@ -844,84 +844,84 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.dtnext.in/news/national/jarange-expresses-confidence-about-marathas-getting-quota-obc-leaders-unhappy-845455</t>
+          <t>https://www.thestatesman.com/india/fadnavis-approves-obc-panel-as-minister-chhagan-bhujbal-skips-cabinet-meeting-1503481064.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/fadnavis-approves-obc-panel-as-minister-chhagan-bhujbal-skips-cabinet-meeting-1503481064.html</t>
+          <t>https://news.careers360.com/west-bengal-teacher-recruitment-2025-wbssc-announces-35726-teaching-posts-including-17-obc-quota</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/west-bengal-teacher-recruitment-2025-wbssc-announces-35726-teaching-posts-including-17-obc-quota</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/03/bom25-mh-quota-bjp-mlc.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/03/bom25-mh-quota-bjp-mlc.html</t>
+          <t>https://www.freepressjournal.in/bhopal/letter-to-madhya-pradesh-advocate-general-for-implementation-of-obc-reservation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/bhopal/letter-to-madhya-pradesh-advocate-general-for-implementation-of-obc-reservation</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-congress-chief-slams-govt-over-hyderabad-gazette-based-maratha-reservation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-congress-chief-slams-govt-over-hyderabad-gazette-based-maratha-reservation</t>
+          <t>https://www.freepressjournal.in/bhopal/union-minister-shivraj-singh-chouhan-vivek-tankha-hold-talks-to-settle-obc-defamation-case</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/bhopal/union-minister-shivraj-singh-chouhan-vivek-tankha-hold-talks-to-settle-obc-defamation-case</t>
+          <t>https://www.socialnews.xyz/?p=6533806</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6533806</t>
+          <t>https://www.sakshipost.com/news/will-maha-govt-grant-42-pc-reservation-backward-classes-telangana-congress-448562</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/will-maha-govt-grant-42-pc-reservation-backward-classes-telangana-congress-448562</t>
+          <t>https://www.thehawk.in/news/india/obcs-to-organise-protest-against-maratha-reservation-under-their-quota</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/obcs-to-organise-protest-against-maratha-reservation-under-their-quota</t>
+          <t>https://www.thehawk.in/news/india/maratha-body-files-caveat-pleading-not-to-give-unilateral-stay-on-reservation-decision</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/maratha-body-files-caveat-pleading-not-to-give-unilateral-stay-on-reservation-decision</t>
+          <t>https://www.thedailyjagran.com/maharashtra/manoj-jarange-warns-of-poll-fallout-if-marathas-are-denied-obc-quota-will-make-them-bite-the-dust-10264841</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.thedailyjagran.com/maharashtra/manoj-jarange-warns-of-poll-fallout-if-marathas-are-denied-obc-quota-will-make-them-bite-the-dust-10264841</t>
+          <t>https://www.freepressjournal.in/mumbai/unjust-illegal-obc-leader-laxman-hake-slams-maha-governments-gr-on-manoj-jaranges-maratha-quota-demands</t>
         </is>
       </c>
     </row>
@@ -935,56 +935,56 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/unjust-illegal-obc-leader-laxman-hake-slams-maha-governments-gr-on-manoj-jaranges-maratha-quota-demands</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/obc-reservation-case-supreme-court-hearing-13-percent-posts-madhya-pradesh-135843416.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/obc-reservation-case-supreme-court-hearing-13-percent-posts-madhya-pradesh-135843416.html</t>
+          <t>https://www.freepressjournal.in/mumbai/bhujbal-skips-cabinet-meet-vows-court-challenge-to-maratha-quota-under-obc-category</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bhujbal-skips-cabinet-meet-vows-court-challenge-to-maratha-quota-under-obc-category</t>
+          <t>https://www.freepressjournal.in/mumbai/maratha-reservation-row-maharashtra-cabinet-decides-to-form-six-member-subcommittee-for-obc-community-issues</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maratha-reservation-row-maharashtra-cabinet-decides-to-form-six-member-subcommittee-for-obc-community-issues</t>
+          <t>https://www.freepressjournal.in/mumbai/govt-has-no-right-to-issue-such-gr-obc-activist-laxman-hake-slams-maha-governments-gr-on-manoj-jaranges-maratha-quota-demands</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/govt-has-no-right-to-issue-such-gr-obc-activist-laxman-hake-slams-maha-governments-gr-on-manoj-jaranges-maratha-quota-demands</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-forms-9-member-cabinet-sub-committee-to-expedite-obc-welfare-address-reservation-issues</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-forms-9-member-cabinet-sub-committee-to-expedite-obc-welfare-address-reservation-issues</t>
+          <t>https://www.bhaskarenglish.in/national/news/maratha-reservation-mahayuti-government-obc-organisations-govt-order-chhagan-bhujbal-135835185.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/maratha-reservation-mahayuti-government-obc-organisations-govt-order-chhagan-bhujbal-135835185.html</t>
+          <t>https://www.thehawk.in/news/india/no-injustice-to-obcs-maharashtra-minister-bawankule-allays-apprehensions</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/no-injustice-to-obcs-maharashtra-minister-bawankule-allays-apprehensions</t>
+          <t>https://www.newsdrum.in/national/jarange-expresses-confidence-about-marathas-getting-quota-obc-leaders-unhappy-9781660</t>
         </is>
       </c>
     </row>

--- a/Output/OBC Andolan/extracted_links.xlsx
+++ b/Output/OBC Andolan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A93"/>
+  <dimension ref="A1:A92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,49 +459,49 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/bengaluru-news/karnataka-reservation-quota-now-at-56-full-breakdown-for-sc-st-and-obc-categories-101756956540466.html</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/obc-leaders-threaten-stir-against-gr-on-maratha-quota-bhujbal-to-move-court/article70009036.ece</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/obc-leaders-threaten-stir-against-gr-on-maratha-quota-bhujbal-to-move-court/article70009036.ece</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maratha-multiple-quotas-prakash-ambedkar-fadnavis-manoj-jarange-patil/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maratha-multiple-quotas-prakash-ambedkar-fadnavis-manoj-jarange-patil/</t>
+          <t>https://www.hindustantimes.com/cities/bengaluru-news/karnataka-reservation-quota-now-at-56-full-breakdown-for-sc-st-and-obc-categories-101756956540466.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.outlookindia.com/national/jarange-patils-maratha-quota-demand-collides-with-obc-groups-hard-won-27</t>
+          <t>https://impressivetimes.com/latest/congress-demands-reservation-private-educational-institutions/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/congress-demands-reservation-private-educational-institutions/</t>
+          <t>https://www.outlookindia.com/national/jarange-patils-maratha-quota-demand-collides-with-obc-groups-hard-won-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/education-today/news/story/reservation-beyond-50-mps-obc-demand-faces-judicial-scrutiny-2781436-2025-09-04</t>
+          <t>https://www.indiatoday.in/india/story/maratha-quota-protest-mumbai-is-manoj-jarange-patil-really-a-achievement-big-historic-win-explained-voices-2781290-2025-09-03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3614925-obc-protest-ends-as-maharashtra-government-commits-to-reservation-protection</t>
+          <t>https://m.thewire.in/article/politics/maratha-reservation-row-highlights-differences-within-bjp-led-mahayuti-govt-in-maharashtra/amp</t>
         </is>
       </c>
     </row>
@@ -515,28 +515,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/obc-fedn-ends-hunger-strike-after-maha-concedes-key-demands/articleshow/123706051.cms</t>
+          <t>https://www.thehindu.com/news/national/modi-govt-must-introduce-law-for-implementing-article-155-in-parliaments-winter-session-congress/article70015720.ece</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/modi-govt-must-introduce-law-for-implementing-article-155-in-parliaments-winter-session-congress/article70015720.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/obc-fedn-ends-hunger-strike-after-maha-concedes-key-demands/articleshow/123706051.cms</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/modi-govt-must-introduce-law-for-implementing-article-155-in-parliaments-winter-session-congress-3713805</t>
+          <t>https://www.indiatoday.in/education-today/news/story/reservation-beyond-50-mps-obc-demand-faces-judicial-scrutiny-2781436-2025-09-04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/telangana/implement-obc-reservations-in-nalsar-and-national-law-schools-sravan-dasoju/article70013458.ece</t>
+          <t>https://www.deccanherald.com/india/modi-govt-must-introduce-law-for-implementing-article-155-in-parliaments-winter-session-congress-3713805</t>
         </is>
       </c>
     </row>
@@ -550,182 +550,182 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/politics/maratha-reservation-row-highlights-differences-within-bjp-led-mahayuti-govt-in-maharashtra/amp</t>
+          <t>https://www.thehindu.com/news/national/telangana/implement-obc-reservations-in-nalsar-and-national-law-schools-sravan-dasoju/article70013458.ece</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/04/maharashtra-congress-urges-cm-fadnavis-to-raise-obc-quota-from-27-to-42-on-telangana-model</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maratha-quota-manoj-jarange-warns-if-betrayed-ruling-parties-will-bite-dust-in-polls-stir-to-continue-in-konkan/articleshow/123714122.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1291262</t>
+          <t>https://www.devdiscourse.com/article/politics/3614925-obc-protest-ends-as-maharashtra-government-commits-to-reservation-protection</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maratha-quota-agitation-activists-end-protest-as-govt-assures-their-quota-would-remain-untouched-3711729</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/sakal-obc-samaj-urges-govt-not-to-yield-to-maratha-quota-demands/articleshow/123619015.cms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/latest-news/fadnavis-breaks-silence-no-injustice-to-obcs-in-hyderabad-gazetteer-gr</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/will-ask-obcs-to-come-under-open-category-cong-mla-wadettiwar/articleshow/123724689.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/sakal-obc-samaj-urges-govt-not-to-yield-to-maratha-quota-demands/articleshow/123619015.cms</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/04/maharashtra-congress-urges-cm-fadnavis-to-raise-obc-quota-from-27-to-42-on-telangana-model</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maratha-quota-protest-mumbai-is-manoj-jarange-patil-really-a-achievement-big-historic-win-explained-voices-2781290-2025-09-03</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maratha-quota-agitation-activists-end-protest-as-govt-assures-their-quota-would-remain-untouched-3711729</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/will-ask-obcs-to-come-under-open-category-cong-mla-wadettiwar/articleshow/123724689.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maratha-quota-issue-maharashtra-minister-chhagan-bhujbal-boycotts-cabinet-meet-3709912</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3615789-maharashtras-balancing-act-maratha-reservation-and-obc-safeguards</t>
+          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1291262</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/devendra-fadnavis-assures-chhagan-bhujbal-of-no-injustice-to-obcs-day-after-ncp-leader-skips-cabinet-meet-maratha-reservation-issue-3712298</t>
+          <t>https://english.lokshahi.com/latest-news/fadnavis-breaks-silence-no-injustice-to-obcs-in-hyderabad-gazetteer-gr</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/will-fadnavis-govt-follow-telangana-model-and-grant-42-pc-quota-to-obcs-asks-sapkal-3267706/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maratha-quota-protest-in-mumbai-stop-pampering-jarange-bhujbal-tells-maharashtra-government-warns-of-obc-protest-if-demands-met/articleshow/123621077.cms</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/have-faith-our-people-in-marathwada-and-western-maharashtra-will-get-reservation-jarange-3709943</t>
+          <t>https://www.deccanherald.com/india/maharashtra/devendra-fadnavis-assures-chhagan-bhujbal-of-no-injustice-to-obcs-day-after-ncp-leader-skips-cabinet-meet-maratha-reservation-issue-3712298</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/amp/story/nation/2025/Sep/04/maharashtra-cm-fadnavis-assures-obcs-that-maratha-quota-move-wont-affect-their-reservations</t>
+          <t>https://www.deccanherald.com/india/karnataka/karnataka-govt-rolls-out-new-quota-roster-general-category-share-down-to-44-3710562</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://english.gujaratsamachar.com/news/gujarat/bjp-mla-says-most-of-the-benefits-of-obc-are-availed-by-affluent-castes-sparks-controversy</t>
+          <t>https://www.deccanherald.com/india/maharashtra/have-faith-our-people-in-marathwada-and-western-maharashtra-will-get-reservation-jarange-3709943</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maratha-quota-issue-maharashtra-minister-chhagan-bhujbal-boycotts-cabinet-meet-3709912</t>
+          <t>https://www.siasat.com/will-fadnavis-govt-follow-telangana-model-and-grant-42-pc-quota-to-obcs-asks-sapkal-3267706/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/04/if-betrayed-over-maratha-quota-we-will-make-them-bite-the-dust-in-polls-jarange-2</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/obc-federation-sees-no-loss-in-maratha-gr-but-demands-talks-before-ending-stir/articleshow/123684651.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/obc-federation-sees-no-loss-in-maratha-gr-but-demands-talks-before-ending-stir/articleshow/123684651.cms</t>
+          <t>https://www.thestatesman.com/india/congress-demands-law-for-reservation-in-private-educational-institutions-1503481991.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maratha-quota-protest-in-mumbai-stop-pampering-jarange-bhujbal-tells-maharashtra-government-warns-of-obc-protest-if-demands-met/articleshow/123621077.cms</t>
+          <t>https://www.newindianexpress.com/amp/story/nation/2025/Sep/04/maharashtra-cm-fadnavis-assures-obcs-that-maratha-quota-move-wont-affect-their-reservations</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/karnataka-govt-rolls-out-new-quota-roster-general-category-share-down-to-44-3710562</t>
+          <t>https://aninews.in/news/national/general-news/gross-betrayal-breach-of-trust-and-violation-of-social-justice-sravan-dasoju-accuses-centre-ugc-of-failing-to-enforce-bc-reservations20250905225143/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maratha-quota-stir-enters-day-2-manoj-jarange-warns-govt-not-to-test-patience-traffic-comes-to-standstill-in-south-mumbai-top-developments/articleshow/123599425.cms</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/03/maratha-community-divided-as-maharashtra-government-issues-gr-on-kunbi-certificates-under-obc-quota</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/congress-demands-law-for-reservation-in-private-educational-institutions-1503481991.html</t>
+          <t>https://english.gujaratsamachar.com/news/gujarat/bjp-mla-says-most-of-the-benefits-of-obc-are-availed-by-affluent-castes-sparks-controversy</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/gross-betrayal-breach-of-trust-and-violation-of-social-justice-sravan-dasoju-accuses-centre-ugc-of-failing-to-enforce-bc-reservations20250905225143/</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/04/if-betrayed-over-maratha-quota-we-will-make-them-bite-the-dust-in-polls-jarange-2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maratha-reservation-issue-settled-bhujbal-was-also-informed-by-cm-eknath-shinde-10230971/</t>
+          <t>https://www.asianage.com/nation/maratha-obc-quota-dispute-sparks-tensions-within-maha-government-1901459</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/no-intent-to-take-away-reservation-of-one-community-and-giving-to-another-cm-fadnavis-2955596.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maratha-reservation-issue-settled-bhujbal-was-also-informed-by-cm-eknath-shinde-10230971/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/03/maratha-community-divided-as-maharashtra-government-issues-gr-on-kunbi-certificates-under-obc-quota</t>
+          <t>https://www.news18.com/videos/breaking-news/maharashtra-protests-over-maratha-reservation-discontent-obc-groups-voice-discontent-news18-9545908.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3613986-maharashtras-maratha-reservation-protest-a-tug-of-obc-identity</t>
+          <t>https://zeenews.india.com/india/no-intent-to-take-away-reservation-of-one-community-and-giving-to-another-cm-fadnavis-2955596.html</t>
         </is>
       </c>
     </row>
@@ -739,112 +739,112 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.asianage.com/nation/maratha-obc-quota-dispute-sparks-tensions-within-maha-government-1901459</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maratha-morcha-no-obc-leader-upset-with-maratha-quota-decision-by-maharashtra-govt-says-bjp-mlc-parinay-fuke-23592332</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://punemirror.com/opinion/editorials/reservation-riddle-maratha-quota-and-the-obc-conundrum/</t>
+          <t>https://www.indianewsstream.com/obcs-must-fight-their-own-battle-instead-of-relying-on-any-leader-prakash-ambedkar/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.indianewsstream.com/obcs-must-fight-their-own-battle-instead-of-relying-on-any-leader-prakash-ambedkar/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/mumbai-maratha-quota-protest-live-updates-manoj-jarange-patil-hunger-strike-fadnavis-cabinet-10223256/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/latest-news/chandrashekhar-bawankule-first-reaction-responsibility-of-the-chairmanship-of-the-obc-sub-committee-in-the-cabinet-ministry-maratha-reservation</t>
+          <t>https://punemirror.com/opinion/editorials/reservation-riddle-maratha-quota-and-the-obc-conundrum/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.news18.com/videos/breaking-news/maharashtra-protests-over-maratha-reservation-discontent-obc-groups-voice-discontent-news18-9545908.html</t>
+          <t>https://english.lokshahi.com/latest-news/chandrashekhar-bawankule-first-reaction-responsibility-of-the-chairmanship-of-the-obc-sub-committee-in-the-cabinet-ministry-maratha-reservation</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/what-is-the-hyderabad-gazette-giving-reservation-to-marathas-kunbi-status-maharashtra-government-maratha-quota-row-2781342-2025-09-03</t>
+          <t>https://www.ptinews.com/story/national/karnataka-reservation-roster-sc-st-obc-quota-at-56-per-cent-general-merit-44-per-cent/2883055</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/karnataka-reservation-roster-sc-st-obc-quota-at-56-per-cent-general-merit-44-per-cent/2883055</t>
+          <t>https://www.devdiscourse.com/article/headlines/3614421-maharashtra-government-moves-ahead-amid-maratha-reservation-developments</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/mumbai-maratha-quota-protest-live-updates-manoj-jarange-patil-hunger-strike-fadnavis-cabinet-10223256/</t>
+          <t>https://www.theweek.in/news/india/2025/09/03/will-take-to-streets-as-jarange-s-hunger-strike-ends-maharashtra-govt-now-faces-ob-cs-ire.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maratha-morcha-no-obc-leader-upset-with-maratha-quota-decision-by-maharashtra-govt-says-bjp-mlc-parinay-fuke-23592332</t>
+          <t>https://udayavani.com/karnataka/karnataka-reservation-roster-scst-obc-quota-at-56-per-cent-general-merit-44-per-cent-20250904T024333663Z?lang=en</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://udayavani.com/karnataka/karnataka-reservation-roster-scst-obc-quota-at-56-per-cent-general-merit-44-per-cent-20250904T024333663Z?lang=en</t>
+          <t>https://www.editorji.com/india-news/maharashtras-kunbi-certificate-controversy-1756883271526</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3614421-maharashtra-government-moves-ahead-amid-maratha-reservation-developments</t>
+          <t>https://www.outlookindia.com/national/maharashtra-government-forms-sub-committee-to-address-obc-welfare-amid-maratha-quota-protests</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/09/03/will-take-to-streets-as-jarange-s-hunger-strike-ends-maharashtra-govt-now-faces-ob-cs-ire.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/03/bes17-mh-quota-obc-protest.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.outlookindia.com/national/maharashtra-government-forms-sub-committee-to-address-obc-welfare-amid-maratha-quota-protests</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/03/maharashtra-minister-bhujbal-to-move-court-against-government-order-on-grant-of-kunbi-certificates-to-marathas</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/03/maharashtra-minister-bhujbal-to-move-court-against-government-order-on-grant-of-kunbi-certificates-to-marathas</t>
+          <t>https://www.thestatesman.com/india/fadnavis-approves-obc-panel-as-minister-chhagan-bhujbal-skips-cabinet-meeting-1503481064.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/03/bes17-mh-quota-obc-protest.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/03/bom25-mh-quota-bjp-mlc.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/fadnavis-approves-obc-panel-as-minister-chhagan-bhujbal-skips-cabinet-meeting-1503481064.html</t>
+          <t>https://www.devdiscourse.com/article/law-order/3613654-maratha-quota-decision-a-balancing-act</t>
         </is>
       </c>
     </row>
@@ -858,21 +858,21 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/03/bom25-mh-quota-bjp-mlc.html</t>
+          <t>https://www.freepressjournal.in/bhopal/letter-to-madhya-pradesh-advocate-general-for-implementation-of-obc-reservation</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/bhopal/letter-to-madhya-pradesh-advocate-general-for-implementation-of-obc-reservation</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-congress-chief-slams-govt-over-hyderabad-gazette-based-maratha-reservation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-congress-chief-slams-govt-over-hyderabad-gazette-based-maratha-reservation</t>
+          <t>https://www.thehawk.in/news/india/obcs-to-organise-protest-against-maratha-reservation-under-their-quota</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/obcs-to-organise-protest-against-maratha-reservation-under-their-quota</t>
+          <t>https://www.freepressjournal.in/mumbai/unjust-illegal-obc-leader-laxman-hake-slams-maha-governments-gr-on-manoj-jaranges-maratha-quota-demands</t>
         </is>
       </c>
     </row>
@@ -914,28 +914,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.thedailyjagran.com/maharashtra/manoj-jarange-warns-of-poll-fallout-if-marathas-are-denied-obc-quota-will-make-them-bite-the-dust-10264841</t>
+          <t>https://www.freepressjournal.in/mumbai/maratha-reservation-row-maharashtra-cabinet-decides-to-form-six-member-subcommittee-for-obc-community-issues</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/unjust-illegal-obc-leader-laxman-hake-slams-maha-governments-gr-on-manoj-jaranges-maratha-quota-demands</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/obc-reservation-case-supreme-court-hearing-13-percent-posts-madhya-pradesh-135843416.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/parbhani-abmpsp-condemns-gr-granting-maratha-reservation-under-obc-submits-memorandum-to-maharashtra-government</t>
+          <t>https://www.thedailyjagran.com/maharashtra/manoj-jarange-warns-of-poll-fallout-if-marathas-are-denied-obc-quota-will-make-them-bite-the-dust-10264841</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/obc-reservation-case-supreme-court-hearing-13-percent-posts-madhya-pradesh-135843416.html</t>
+          <t>https://www.freepressjournal.in/pune/parbhani-abmpsp-condemns-gr-granting-maratha-reservation-under-obc-submits-memorandum-to-maharashtra-government</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maratha-reservation-row-maharashtra-cabinet-decides-to-form-six-member-subcommittee-for-obc-community-issues</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-forms-9-member-cabinet-sub-committee-to-expedite-obc-welfare-address-reservation-issues</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-forms-9-member-cabinet-sub-committee-to-expedite-obc-welfare-address-reservation-issues</t>
+          <t>https://www.newsdrum.in/national/jarange-expresses-confidence-about-marathas-getting-quota-obc-leaders-unhappy-9781660</t>
         </is>
       </c>
     </row>
@@ -977,56 +977,56 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/no-injustice-to-obcs-maharashtra-minister-bawankule-allays-apprehensions</t>
+          <t>https://www.thehawk.in/news/india/bhujbal-urges-obc-leaders-to-halt-protests-over-maratha-kunbi-status-mulls-legal-options</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/jarange-expresses-confidence-about-marathas-getting-quota-obc-leaders-unhappy-9781660</t>
+          <t>https://www.thehawk.in/news/india/no-injustice-to-obcs-maharashtra-minister-bawankule-allays-apprehensions</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/bhujbal-urges-obc-leaders-to-halt-protests-over-maratha-kunbi-status-mulls-legal-options</t>
+          <t>https://english.newstrack.com/india-news/hyderabad-gazette-maratha-reservation-538707</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://english.newstrack.com/india-news/hyderabad-gazette-maratha-reservation-538707</t>
+          <t>https://english.varthabharati.in/index.php/karnataka/karnataka-reservation-roster-scst-obc-quota-at-56-per-cent-general-merit-44-per-cent</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/index.php/karnataka/karnataka-reservation-roster-scst-obc-quota-at-56-per-cent-general-merit-44-per-cent</t>
+          <t>https://kknlive.com/en/political-news/congress-targets-modi-government-ahead-of-bihar-elections/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://kknlive.com/en/political-news/congress-targets-modi-government-ahead-of-bihar-elections/</t>
+          <t>https://www.hindustantimes.com/india-news/chhagan-bhujbal-says-will-challenge-gr-on-maratha-quota-in-court-101756910519244.html</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/chhagan-bhujbal-says-will-challenge-gr-on-maratha-quota-in-court-101756910519244.html</t>
+          <t>https://www.msn.com/en-in/news/India/jarange-exults-bhujbal-sulks-minister-skips-cabinet-meet-says-will-challenge-maratha-quota-gr/ar-AA1LNGX4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3615625-maratha-quota-movement-a-call-for-justice-and-inclusion</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/bhujbal-appeals-to-people-to-desist-from-agitations/articleshow/123703527.cms</t>
         </is>
       </c>
     </row>
@@ -1047,33 +1047,26 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://english.metrovaartha.com/news/states/jarange-exults-bhujbal-sulks-minister-skips-cabinet-meet-says-will-challenge-maratha-quota-gr</t>
+          <t>https://telanganatoday.com/obc-activist-warns-of-street-protests-over-maratha-quota-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://telanganatoday.com/obc-activist-warns-of-street-protests-over-maratha-quota-in-maharashtra</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/obc-activist-to-hold-rally-in-baramati-today/articleshow/123704074.cms</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/obc-activist-to-hold-rally-in-baramati-today/articleshow/123704074.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bhujbal-skips-cabinet-meet-says-will-challenge-gr-in-court-101756926793110.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bhujbal-skips-cabinet-meet-says-will-challenge-gr-in-court-101756926793110.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
         <is>
           <t>https://timesofindia.indiatimes.com/city/pune/bhujbal-obc-activists-warn-of-protest-say-gr-allows-marathas-indirect-entry-to-get-their-quota-benefits/articleshow/123663963.cms</t>
         </is>
